--- a/outputs/q1/tables/Q1_定位实验.xlsx
+++ b/outputs/q1/tables/Q1_定位实验.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr/>
   <bookViews>
-    <workbookView tabRatio="500"/>
+    <workbookView firstSheet="1" activeTab="1" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" name="定位实验" sheetId="1"/>
@@ -709,8 +709,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="171" formatCode="0.000000"/>
-    <numFmt numFmtId="172" formatCode="0.000000000"/>
+    <numFmt numFmtId="19321" formatCode="0.000000"/>
+    <numFmt numFmtId="19322" formatCode="0.000000000"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -785,12 +785,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF0DF"/>
+        <fgColor theme="4" tint="0.8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.8"/>
+        <fgColor rgb="FFFFF0DF"/>
       </patternFill>
     </fill>
     <fill>
@@ -866,40 +866,40 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="2" fillId="4" borderId="2" xfId="0">
+    <xf numFmtId="19321" fontId="2" fillId="3" borderId="2" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="2" fillId="4" borderId="3" xfId="0">
+    <xf numFmtId="19322" fontId="2" fillId="3" borderId="3" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="2" xfId="0">
+    <xf numFmtId="19321" fontId="2" fillId="0" borderId="2" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="3" xfId="0">
+    <xf numFmtId="19322" fontId="2" fillId="0" borderId="3" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="2" fillId="3" borderId="2" xfId="0">
+    <xf numFmtId="19321" fontId="2" fillId="4" borderId="2" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="2" fillId="3" borderId="3" xfId="0">
+    <xf numFmtId="19322" fontId="2" fillId="4" borderId="3" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="2" fillId="4" borderId="2" xfId="0">
+    <xf numFmtId="19322" fontId="2" fillId="3" borderId="2" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="2" xfId="0">
+    <xf numFmtId="19322" fontId="2" fillId="0" borderId="2" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0">
@@ -913,7 +913,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="19321" fontId="2" fillId="0" borderId="0" xfId="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1258,7 +1258,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{FD2FFBA6-3B77-4E43-B3CD-4000A0483DCB}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{BD85F02D-D147-4ABE-967C-82A1CAF637C3}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <tabColor rgb="FF17365D"/>
   </sheetPr>
@@ -8441,7 +8441,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{70C28C17-91CF-47F2-B2BF-4CED905E9064}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{99E7732E-0E02-4928-AF91-3F142B90252B}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:T399"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -21141,7 +21141,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{A42DDCDD-3A98-4D81-8637-5756DE5A8A7B}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{58C9D580-7B57-4DC6-8652-89864906F449}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:T200"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
